--- a/data/Oficina_de_procuradora_de_mujeres/opmServiciosMes.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmServiciosMes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC73137-4BEC-4AC8-91AB-7CC7DF1BAA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B76275-18D3-46AC-A2E2-A9393924AB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="1560" windowWidth="17280" windowHeight="9420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -462,7 +462,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>917</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -539,7 +539,7 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>433</v>
+        <v>962</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -616,7 +616,7 @@
         <v>2</v>
       </c>
       <c r="C22">
-        <v>499</v>
+        <v>1163</v>
       </c>
     </row>
   </sheetData>

--- a/data/Oficina_de_procuradora_de_mujeres/opmServiciosMes.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmServiciosMes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B76275-18D3-46AC-A2E2-A9393924AB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8B78E2-D789-4796-B6C3-03EC2A1FE818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11196" yWindow="2028" windowWidth="10764" windowHeight="9420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -462,7 +462,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>1917</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -539,7 +539,7 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>962</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -616,7 +616,7 @@
         <v>2</v>
       </c>
       <c r="C22">
-        <v>1163</v>
+        <v>1402</v>
       </c>
     </row>
   </sheetData>

--- a/data/Oficina_de_procuradora_de_mujeres/opmServiciosMes.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmServiciosMes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8B78E2-D789-4796-B6C3-03EC2A1FE818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E862444-2E2C-4C8A-9F19-3764F1D60B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11196" yWindow="2028" windowWidth="10764" windowHeight="9420" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10416" yWindow="2412" windowWidth="12132" windowHeight="9384" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -462,7 +462,7 @@
         <v>3</v>
       </c>
       <c r="C8">
-        <v>2310</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -539,7 +539,7 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>1129</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
